--- a/p6_deployment/data/germany/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/germany/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:BN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,6 +568,196 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -674,6 +864,120 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
+      <c r="AC2" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>185.0909090909091</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2527272.727272727</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>28.18181818181818</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2870454.545454545</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>73.72727272727273</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>24.08333333333333</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>67.54166666666667</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1840625</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>183.0952380952381</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3064285.714285714</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>74.38095238095238</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>123</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>425</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>438</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -780,6 +1084,120 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="AC3" t="n">
+        <v>28.09090909090909</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3659090.909090909</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>73.81818181818181</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>185.0909090909091</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2527272.727272727</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>27.28571428571428</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>182.5238095238095</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2392857.142857143</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>73.95238095238095</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>23.29166666666667</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2278125</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>73.45833333333333</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>425</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>438</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>123</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -882,6 +1300,106 @@
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>81.11111111111111</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>31833333.33333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>84.66666666666667</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>185.3636363636364</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5965909.090909091</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>76.72727272727273</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>23.45454545454545</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2.045454545454545</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>80.09090909090909</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>39372727.27272727</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>84.59090909090909</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>183.2631578947368</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>71.68421052631579</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5056578.947368421</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>77.47368421052632</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>585</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>603</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -988,6 +1506,120 @@
           <t>8vndvXTk</t>
         </is>
       </c>
+      <c r="AC5" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>183.6363636363636</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.545454545454545</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>81.36363636363636</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>31090909.09090909</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>83.72727272727273</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2606818.181818182</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>74.09090909090909</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>24.34782608695652</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>184.0434782608696</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>79.17391304347827</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>26413043.47826087</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>83.04347826086956</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>25.08695652173913</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>184.5652173913043</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>68.52173913043478</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1985869.565217391</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>72.69565217391305</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>296</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>43500000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>323</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>696</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>19200000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1094,6 +1726,120 @@
           <t>nP1i5US1</t>
         </is>
       </c>
+      <c r="AC6" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>78</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>79.54545454545455</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>28227272.72727273</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>83.63636363636364</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>74.15000000000001</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7136250</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>185.5714285714286</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.80952380952381</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>74.42857142857143</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15653571.42857143</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>81.0952380952381</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>186.75</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>275</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>24275000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>315</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>237</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>82300000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>243</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1196,6 +1942,120 @@
           <t>88HSzjDr</t>
         </is>
       </c>
+      <c r="AC7" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>186.5454545454545</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>73</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4563636.363636363</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>185.8181818181818</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>6427272.727272728</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>77.63636363636364</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>27.47619047619047</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>183.6190476190476</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>70.28571428571429</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>72.04761904761905</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>186</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>68.91666666666667</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2897500</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>75.04166666666667</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>188.6666666666667</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>197</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>211</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>186.1666666666667</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>426</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>454</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1298,6 +2158,120 @@
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.909090909090909</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9436363.636363637</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>185.7272727272727</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>81.27272727272727</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>33018181.81818182</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>71.61904761904762</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5745238.095238095</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>79.66666666666667</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>70.41666666666667</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7018750</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>81.41666666666667</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>296</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>33900000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>321</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>804</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>502550000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1404,6 +2378,120 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="AC9" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12645454.54545454</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>79.27272727272727</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>183.0833333333333</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>71.91666666666667</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5502083.333333333</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>75.08333333333333</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>22.69565217391304</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>183.695652173913</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.304347826086957</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4823913.043478261</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>78.21739130434783</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>346</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>24775000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>389</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>284</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>23125000</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1506,6 +2594,120 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
+      <c r="AC10" t="n">
+        <v>26.81818181818182</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>8590909.090909092</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>183</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>74.90909090909091</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>8372727.272727272</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>77.18181818181819</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>25.70833333333333</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>183.0416666666667</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>73.95833333333333</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5981250</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>76.70833333333333</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>26.16666666666667</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>183.1666666666667</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>74.22222222222223</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6561111.111111111</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>76.22222222222223</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>186.75</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>293</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>16875000</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>293</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>449</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>61800000</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>465</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1612,6 +2814,120 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
+      <c r="AC11" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4909090.909090909</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>185.9090909090909</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>3538636.363636364</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>183.4166666666667</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>70.54166666666667</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3071875</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>75.79166666666667</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>28.04761904761905</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>71.71428571428571</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2680952.380952381</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>26.57142857142857</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>481</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>503</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1718,6 +3034,120 @@
           <t>8vndvXTk</t>
         </is>
       </c>
+      <c r="AC12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11620000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>182.0909090909091</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>6945454.545454546</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>78.72727272727273</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>25.93333333333333</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>184.1333333333333</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8661666.666666666</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>26.45833333333333</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>185</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>73.91666666666667</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5830208.333333333</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>77.20833333333333</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>366</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>50325000</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>400</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>145</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1824,6 +3254,120 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="AC13" t="n">
+        <v>28.81818181818182</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>183</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>73.81818181818181</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3711363.636363636</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>74.81818181818181</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>187.0909090909091</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>79.45454545454545</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>23881818.18181818</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>83.18181818181819</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>26.23809523809524</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>184.5714285714286</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2526190.476190476</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>74.0952380952381</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>23.94117647058824</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>180.2352941176471</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.588235294117647</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>77.47058823529412</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>25211764.70588235</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>83.11764705882354</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>26.83333333333333</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>413</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>8700000</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>432</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>177</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>87</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>118500000</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1926,6 +3470,120 @@
           <t>dfNCCCzS</t>
         </is>
       </c>
+      <c r="AC14" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>183.6363636363636</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.636363636363636</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>79.18181818181819</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>28418181.81818182</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>84.72727272727273</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>77</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>13700000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>81</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>78.9375</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>27057812.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>83.375</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>22.91304347826087</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>184.8695652173913</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>71.78260869565217</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6240217.391304348</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>79.26086956521739</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>643</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>451550000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>670</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>228</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>243</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2032,6 +3690,120 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
+      <c r="AC15" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>185.6363636363636</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2670454.545454545</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.909090909090909</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>9436363.636363637</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>27.58333333333333</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>186.2916666666667</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>69.54166666666667</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1592708.333333333</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>71.04166666666667</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>184.9583333333333</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>71</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5306250</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>566</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>589</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>296</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>33900000</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>321</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2138,6 +3910,120 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
+      <c r="AC16" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.636363636363636</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>74.36363636363636</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>6936363.636363637</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>78.81818181818181</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>21930000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.523809523809524</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>72.19047619047619</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4377380.952380952</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>77.61904761904762</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>22.54166666666667</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>180.4583333333333</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.708333333333333</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>74.625</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>18862500</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>81.08333333333333</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>293</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>298</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>225</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>40700000</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>246</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2244,6 +4130,120 @@
           <t>EuakNmc1</t>
         </is>
       </c>
+      <c r="AC17" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.636363636363636</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10927272.72727273</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>17550000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>26.26086956521739</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>182.695652173913</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.565217391304348</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>74</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6639130.434782608</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>76.34782608695652</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>183.3684210526316</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>72.21052631578948</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6440789.47368421</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>79.26315789473684</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>214</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>16150000</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>231</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>351</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>29275000</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>391</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2346,6 +4346,120 @@
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>185.3636363636364</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>5827272.727272728</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>28.09090909090909</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>184.1818181818182</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>76</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>8209090.909090909</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>77.72727272727273</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>70.04166666666667</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3378750</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>75.54166666666667</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>26.79166666666667</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.458333333333333</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>74.29166666666667</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>5897916.666666667</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>76.29166666666667</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>354</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>13450000</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>363</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>142</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>5575000</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2448,6 +4562,120 @@
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>75.81818181818181</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>9309090.909090908</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>185.8181818181818</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>4034090.909090909</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75.09090909090909</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>25.72222222222222</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>184.5555555555555</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>73.05555555555556</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5122222.222222222</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>75.72222222222223</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>70.08333333333333</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>2551041.666666667</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>71.79166666666667</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>376</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>59800000</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>392</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>190</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>272</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>286</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2554,6 +4782,120 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
+      <c r="AC20" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>79.63636363636364</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>23818181.81818182</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>82.63636363636364</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>4909090.909090909</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>185.6086956521739</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.608695652173913</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>75.82608695652173</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>14963043.47826087</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>80.60869565217391</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>26.56521739130435</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>185.0869565217391</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.217391304347826</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>71.78260869565217</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3448913.043478261</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>74.78260869565217</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>246</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>259</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>188.6666666666667</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>219</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2656,6 +4998,120 @@
           <t>fiEQZ7C7</t>
         </is>
       </c>
+      <c r="AC21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>74.36363636363636</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>6445454.545454546</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>76.81818181818181</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>12572727.27272727</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>79.81818181818181</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>23.38095238095238</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.095238095238095</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>71.57142857142857</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4432142.857142857</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>77.47619047619048</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>182.9047619047619</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>72.42857142857143</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>5815476.19047619</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>76.04761904761905</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>435</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>450</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>347</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>24475000</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>387</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2758,6 +5214,68 @@
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>67.09090909090909</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1252272.727272727</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>182.4166666666667</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>65.45833333333333</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1076041.666666667</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2860,6 +5378,68 @@
           <t>EuakNmc1</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>186.2727272727273</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>66.90909090909091</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1140909.090909091</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>183.5416666666667</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2962,6 +5542,92 @@
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>184.0909090909091</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2320454.545454545</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>72.90909090909091</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1994444.444444444</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>67.41666666666667</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2019375</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>73.83333333333333</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>178.8333333333333</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>66.05555555555556</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1291666.666666667</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3064,6 +5730,92 @@
           <t>naWckLmC</t>
         </is>
       </c>
+      <c r="AC25" t="n">
+        <v>27.09090909090909</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1157727.272727273</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1579545.454545455</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>180.1052631578947</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>65.89473684210526</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>962368.4210526316</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>67.84210526315789</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>27.45833333333333</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1363541.666666667</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>71.41666666666667</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -3170,6 +5922,92 @@
           <t>nP1i5US1</t>
         </is>
       </c>
+      <c r="AC26" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>69.36363636363636</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2318181.818181818</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>75.09090909090909</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1642500</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>24.42857142857143</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>182.4285714285714</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>66.52380952380952</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1663095.238095238</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>72.52380952380952</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>26.92307692307692</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>183.5384615384615</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>67.23076923076923</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1271538.461538462</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>70.92307692307692</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -3276,6 +6114,92 @@
           <t>CCQGbik8</t>
         </is>
       </c>
+      <c r="AC27" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>23.45454545454545</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>182.9090909090909</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>65.90909090909091</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1406818.181818182</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>24.13636363636364</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>179.8636363636364</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2404545.454545455</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>73.72727272727273</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>28.31818181818182</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>182.8636363636364</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>67.40909090909091</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1036363.636363636</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>68.59090909090909</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -3382,6 +6306,92 @@
           <t>ILyJuN3g</t>
         </is>
       </c>
+      <c r="AC28" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2009090.909090909</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>186.5454545454545</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1604545.454545455</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>25.19047619047619</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>183.4761904761905</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1670238.095238095</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>71.71428571428571</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>24.78260869565218</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>184.5217391304348</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>67.43478260869566</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>72.43478260869566</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -3484,6 +6494,92 @@
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>184.9090909090909</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1281818.181818182</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>23.27272727272727</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>186.6363636363636</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1477272.727272727</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>25.19047619047619</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>182.8571428571429</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>66.76190476190476</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1220238.095238095</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>70.19047619047619</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>25.95454545454545</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>186.4090909090909</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>67.31818181818181</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1418181.818181818</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>70.68181818181819</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -3586,6 +6682,92 @@
           <t>dfNCCCzS</t>
         </is>
       </c>
+      <c r="AC30" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>184.0909090909091</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>68.54545454545455</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1638636.363636364</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>24.36363636363636</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1386363.636363636</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>25.8695652173913</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>182.7826086956522</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>67.52173913043478</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1417173.913043478</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>70.26086956521739</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>26.29166666666667</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>66.375</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1155416.666666667</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>68.625</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -3684,6 +6866,92 @@
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>184.4583333333333</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>65.875</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1358333.333333333</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>69.91666666666667</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>28.05263157894737</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>183.421052631579</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>69.21052631578948</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1543421.052631579</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>72.05263157894737</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -3790,6 +7058,92 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
+      <c r="AC32" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>186.2727272727273</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>66.90909090909091</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1140909.090909091</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>185.6363636363636</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>69.54545454545455</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>2045454.545454545</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>65.08333333333333</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1064583.333333333</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>25.31578947368421</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>185.8947368421053</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>66.31578947368421</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1280263.157894737</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>71.21052631578948</v>
+      </c>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3896,6 +7250,92 @@
           <t>EuakNmc1</t>
         </is>
       </c>
+      <c r="AC33" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>67.72727272727273</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1525000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>186.5454545454545</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>67.72727272727273</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1220454.545454545</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>26.95833333333333</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1301041.666666667</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>69.95833333333333</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>64.875</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1015625</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -4002,6 +7442,92 @@
           <t>QqLCC3il</t>
         </is>
       </c>
+      <c r="AC34" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1734090.909090909</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>73.63636363636364</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1868181.818181818</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>73.81818181818181</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>29.375</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>182.0833333333333</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>68.41666666666667</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1137500</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>24.72222222222222</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>183.1666666666667</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>66.83333333333333</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1394444.444444444</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>71.22222222222223</v>
+      </c>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -4104,6 +7630,92 @@
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>185.8181818181818</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>70.72727272727273</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2336363.636363636</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1082500</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1536250</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>183.9583333333333</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>65.95833333333333</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1191666.666666667</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>69.83333333333333</v>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -4210,6 +7822,92 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="AC36" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>187.8181818181818</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>68.09090909090909</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1713636.363636364</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>184.1818181818182</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>2845454.545454545</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>74.18181818181819</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>25.52380952380953</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>184</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>67.38095238095238</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1547619.047619048</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>67.95833333333333</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1872916.666666667</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>73.20833333333333</v>
+      </c>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -4308,6 +8006,92 @@
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>183</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2760000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1790909.090909091</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>26.60869565217391</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>183.3478260869565</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.391304347826087</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>68.91304347826087</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1661956.52173913</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>73.30434782608695</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1513500</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -4410,6 +8194,92 @@
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1786363.636363636</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>73.90909090909091</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>67.54545454545455</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1365909.090909091</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>26.45833333333333</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>182.2083333333333</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1205208.333333333</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>69.70833333333333</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1019250</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -4516,6 +8386,92 @@
           <t>ILyJuN3g</t>
         </is>
       </c>
+      <c r="AC39" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>188</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1512500</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>184.0909090909091</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1263636.363636364</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>69.90909090909091</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>25.54166666666667</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>185.4166666666667</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>67.41666666666667</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1456458.333333333</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>72.58333333333333</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>25.78260869565218</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>183.5652173913043</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>67.08695652173913</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1243478.260869565</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>69.78260869565217</v>
+      </c>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -4618,6 +8574,92 @@
           <t>6FDqshzF</t>
         </is>
       </c>
+      <c r="AC40" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>181</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2066666.666666667</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>69.36363636363636</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>2318181.818181818</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>75.09090909090909</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>65.73333333333333</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1438888.888888889</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>72.61111111111111</v>
+      </c>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -4720,6 +8762,92 @@
           <t>ILyJuN3g</t>
         </is>
       </c>
+      <c r="AC41" t="n">
+        <v>23.27272727272727</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>186.5454545454545</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>66.36363636363636</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1477272.727272727</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>25.60869565217391</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>185.0869565217391</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>66.95652173913044</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1358695.652173913</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>70.91304347826087</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>25.08333333333333</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>182.5416666666667</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>70.45833333333333</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>2583333.333333333</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>73.54166666666667</v>
+      </c>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -4820,6 +8948,92 @@
           <t>nP1i5US1</t>
         </is>
       </c>
+      <c r="AC42" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1612500</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>184.9166666666667</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1215625</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1571041.666666667</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>73.41666666666667</v>
+      </c>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/germany/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/germany/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN42"/>
+  <dimension ref="A1:BN43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54600</v>
+        <v>47000</v>
       </c>
       <c r="F2" t="n">
         <v>51500</v>
@@ -834,12 +834,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -883,22 +883,22 @@
         <v>73.36363636363636</v>
       </c>
       <c r="AI2" t="n">
-        <v>28.18181818181818</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>184.4545454545455</v>
+        <v>183.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.090909090909091</v>
+        <v>1.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>71.90909090909091</v>
+        <v>71.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>2870454.545454545</v>
+        <v>2857500</v>
       </c>
       <c r="AN2" t="n">
-        <v>73.72727272727273</v>
+        <v>73.8</v>
       </c>
       <c r="AO2" t="n">
         <v>24.08333333333333</v>
@@ -919,22 +919,22 @@
         <v>72.625</v>
       </c>
       <c r="AU2" t="n">
-        <v>25.66666666666667</v>
+        <v>25.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>183.0952380952381</v>
+        <v>182.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.142857142857143</v>
+        <v>1.15</v>
       </c>
       <c r="AX2" t="n">
-        <v>70.66666666666667</v>
+        <v>70.55</v>
       </c>
       <c r="AY2" t="n">
-        <v>3064285.714285714</v>
+        <v>3067500</v>
       </c>
       <c r="AZ2" t="n">
-        <v>74.38095238095238</v>
+        <v>74.45</v>
       </c>
       <c r="BA2" t="n">
         <v>19.5</v>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1085,22 +1085,22 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>28.09090909090909</v>
+        <v>27.88888888888889</v>
       </c>
       <c r="AD3" t="n">
-        <v>183.4545454545455</v>
+        <v>181.8888888888889</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.181818181818182</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AF3" t="n">
-        <v>72.81818181818181</v>
+        <v>72.77777777777777</v>
       </c>
       <c r="AG3" t="n">
-        <v>3659090.909090909</v>
+        <v>3827777.777777778</v>
       </c>
       <c r="AH3" t="n">
-        <v>73.81818181818181</v>
+        <v>74</v>
       </c>
       <c r="AI3" t="n">
         <v>26.36363636363636</v>
@@ -1121,22 +1121,22 @@
         <v>73.36363636363636</v>
       </c>
       <c r="AO3" t="n">
-        <v>27.28571428571428</v>
+        <v>27.15</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.5238095238095</v>
+        <v>181.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.047619047619048</v>
+        <v>1.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>2392857.142857143</v>
+        <v>2362500</v>
       </c>
       <c r="AT3" t="n">
-        <v>73.95238095238095</v>
+        <v>74</v>
       </c>
       <c r="AU3" t="n">
         <v>23.29166666666667</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>hAcTWKK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2VSFgl3</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1301,22 +1301,22 @@
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>185.6666666666667</v>
+        <v>184.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.777777777777778</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>81.11111111111111</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>31833333.33333333</v>
+        <v>35200000</v>
       </c>
       <c r="AH4" t="n">
-        <v>84.66666666666667</v>
+        <v>84.8</v>
       </c>
       <c r="AI4" t="n">
         <v>25</v>
@@ -1337,40 +1337,40 @@
         <v>76.72727272727273</v>
       </c>
       <c r="AO4" t="n">
-        <v>23.45454545454545</v>
+        <v>23.60869565217391</v>
       </c>
       <c r="AP4" t="n">
-        <v>182.5454545454545</v>
+        <v>182.0434782608696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.045454545454545</v>
+        <v>2.08695652173913</v>
       </c>
       <c r="AR4" t="n">
-        <v>80.09090909090909</v>
+        <v>80.34782608695652</v>
       </c>
       <c r="AS4" t="n">
-        <v>39372727.27272727</v>
+        <v>40508695.65217391</v>
       </c>
       <c r="AT4" t="n">
-        <v>84.59090909090909</v>
+        <v>84.65217391304348</v>
       </c>
       <c r="AU4" t="n">
-        <v>23.57894736842105</v>
+        <v>23.61111111111111</v>
       </c>
       <c r="AV4" t="n">
-        <v>183.2631578947368</v>
+        <v>182.9444444444445</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.052631578947368</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX4" t="n">
-        <v>71.68421052631579</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AY4" t="n">
-        <v>5056578.947368421</v>
+        <v>5093055.555555556</v>
       </c>
       <c r="AZ4" t="n">
-        <v>77.47368421052632</v>
+        <v>77.38888888888889</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1380,25 +1380,25 @@
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>25.375</v>
+        <v>25.57142857142857</v>
       </c>
       <c r="BI4" t="n">
-        <v>183.5</v>
+        <v>184.4285714285714</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.25</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="BK4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
-        <v>585</v>
+        <v>511</v>
       </c>
       <c r="BM4" t="n">
-        <v>37500000</v>
+        <v>31500000</v>
       </c>
       <c r="BN4" t="n">
-        <v>603</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>81365</v>
+        <v>62000</v>
       </c>
       <c r="F5" t="n">
         <v>81365</v>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Q1njn0V</t>
+          <t>Q1njn0Vm</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>MDhPV0R</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1525,40 +1525,40 @@
         <v>83.72727272727273</v>
       </c>
       <c r="AI5" t="n">
-        <v>26.90909090909091</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>186.1818181818182</v>
+        <v>187.2</v>
       </c>
       <c r="AK5" t="n">
         <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>71.36363636363636</v>
+        <v>71.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>2606818.181818182</v>
+        <v>2517500</v>
       </c>
       <c r="AN5" t="n">
-        <v>74.09090909090909</v>
+        <v>74</v>
       </c>
       <c r="AO5" t="n">
-        <v>24.34782608695652</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AP5" t="n">
-        <v>184.0434782608696</v>
+        <v>184.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2</v>
+        <v>1.958333333333333</v>
       </c>
       <c r="AR5" t="n">
-        <v>79.17391304347827</v>
+        <v>79</v>
       </c>
       <c r="AS5" t="n">
-        <v>26413043.47826087</v>
+        <v>25429166.66666667</v>
       </c>
       <c r="AT5" t="n">
-        <v>83.04347826086956</v>
+        <v>82.70833333333333</v>
       </c>
       <c r="AU5" t="n">
         <v>25.08695652173913</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58000</v>
+        <v>47000</v>
       </c>
       <c r="F6" t="n">
         <v>57500</v>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>UgdQz0f</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>pfoInmc</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>24.81818181818182</v>
+        <v>24.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>183.5454545454545</v>
+        <v>183</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.818181818181818</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>16500000</v>
+        <v>16350000</v>
       </c>
       <c r="AH6" t="n">
-        <v>81.45454545454545</v>
+        <v>81.3</v>
       </c>
       <c r="AI6" t="n">
         <v>24.36363636363636</v>
@@ -1820,25 +1820,25 @@
         <v>315</v>
       </c>
       <c r="BH6" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>178</v>
+        <v>177.5</v>
       </c>
       <c r="BJ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK6" t="n">
         <v>2</v>
       </c>
-      <c r="BK6" t="n">
-        <v>3</v>
-      </c>
       <c r="BL6" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="BM6" t="n">
-        <v>82300000</v>
+        <v>31800000</v>
       </c>
       <c r="BN6" t="n">
-        <v>243</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>8W0vrAR</t>
+          <t>8W0vrAR9</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>lGJdeem</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>KUx4Q7x</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>CQTUFgP</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60449</v>
+        <v>54800</v>
       </c>
       <c r="F9" t="n">
         <v>60058</v>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>GzfvcwR</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>M5BRZDs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2397,58 +2397,58 @@
         <v>79.27272727272727</v>
       </c>
       <c r="AI9" t="n">
-        <v>25.5</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>184.3</v>
+        <v>184.1111111111111</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.6</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AL9" t="n">
-        <v>75.59999999999999</v>
+        <v>75.11111111111111</v>
       </c>
       <c r="AM9" t="n">
-        <v>9700000</v>
+        <v>8388888.888888888</v>
       </c>
       <c r="AN9" t="n">
-        <v>78.8</v>
+        <v>78.55555555555556</v>
       </c>
       <c r="AO9" t="n">
-        <v>25.25</v>
+        <v>25.42857142857143</v>
       </c>
       <c r="AP9" t="n">
-        <v>183.0833333333333</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.291666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AR9" t="n">
-        <v>71.91666666666667</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="AS9" t="n">
-        <v>5502083.333333333</v>
+        <v>6045238.095238095</v>
       </c>
       <c r="AT9" t="n">
-        <v>75.08333333333333</v>
+        <v>75.52380952380952</v>
       </c>
       <c r="AU9" t="n">
-        <v>22.69565217391304</v>
+        <v>21.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>183.695652173913</v>
+        <v>184.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.304347826086957</v>
+        <v>1.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>69.56521739130434</v>
+        <v>69.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>4823913.043478261</v>
+        <v>5352500</v>
       </c>
       <c r="AZ9" t="n">
-        <v>78.21739130434783</v>
+        <v>79.45</v>
       </c>
       <c r="BA9" t="n">
         <v>21.2</v>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>v9WoiHG</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>l0fHXMd</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -2649,22 +2649,22 @@
         <v>76.70833333333333</v>
       </c>
       <c r="AU10" t="n">
-        <v>26.16666666666667</v>
+        <v>26.10526315789474</v>
       </c>
       <c r="AV10" t="n">
-        <v>183.1666666666667</v>
+        <v>183.5263157894737</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.555555555555556</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="AX10" t="n">
-        <v>74.22222222222223</v>
+        <v>74.10526315789474</v>
       </c>
       <c r="AY10" t="n">
-        <v>6561111.111111111</v>
+        <v>6342105.263157895</v>
       </c>
       <c r="AZ10" t="n">
-        <v>76.22222222222223</v>
+        <v>76.15789473684211</v>
       </c>
       <c r="BA10" t="n">
         <v>29.75</v>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>4fuCGs9</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="W11" t="n">
@@ -2833,22 +2833,22 @@
         <v>76.09090909090909</v>
       </c>
       <c r="AI11" t="n">
-        <v>27.72727272727273</v>
+        <v>27.44444444444444</v>
       </c>
       <c r="AJ11" t="n">
-        <v>185.9090909090909</v>
+        <v>184.8888888888889</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.181818181818182</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AL11" t="n">
-        <v>73.18181818181819</v>
+        <v>73.22222222222223</v>
       </c>
       <c r="AM11" t="n">
-        <v>3538636.363636364</v>
+        <v>3680555.555555556</v>
       </c>
       <c r="AN11" t="n">
-        <v>75.45454545454545</v>
+        <v>76</v>
       </c>
       <c r="AO11" t="n">
         <v>25.125</v>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>f3ddUIX</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>vZA6VYp</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="W12" t="n">
@@ -3107,25 +3107,25 @@
         <v>77.20833333333333</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="BB12" t="n">
-        <v>185</v>
+        <v>183.8333333333333</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>366</v>
+        <v>440</v>
       </c>
       <c r="BF12" t="n">
-        <v>50325000</v>
+        <v>55225000</v>
       </c>
       <c r="BG12" t="n">
-        <v>400</v>
+        <v>476</v>
       </c>
       <c r="BH12" t="n">
         <v>28</v>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>hAcTWKK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="W13" t="n">
@@ -3255,76 +3255,76 @@
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>28.81818181818182</v>
+        <v>28.77777777777778</v>
       </c>
       <c r="AD13" t="n">
-        <v>183</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.272727272727273</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF13" t="n">
-        <v>73.81818181818181</v>
+        <v>74</v>
       </c>
       <c r="AG13" t="n">
-        <v>3711363.636363636</v>
+        <v>3891666.666666667</v>
       </c>
       <c r="AH13" t="n">
-        <v>74.81818181818181</v>
+        <v>75.22222222222223</v>
       </c>
       <c r="AI13" t="n">
-        <v>25.36363636363636</v>
+        <v>25.9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>187.0909090909091</v>
+        <v>188.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.818181818181818</v>
+        <v>1.9</v>
       </c>
       <c r="AL13" t="n">
-        <v>79.45454545454545</v>
+        <v>80.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>23881818.18181818</v>
+        <v>25950000</v>
       </c>
       <c r="AN13" t="n">
-        <v>83.18181818181819</v>
+        <v>83.3</v>
       </c>
       <c r="AO13" t="n">
-        <v>26.23809523809524</v>
+        <v>25.94736842105263</v>
       </c>
       <c r="AP13" t="n">
-        <v>184.5714285714286</v>
+        <v>183.9473684210526</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.047619047619048</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AR13" t="n">
-        <v>71</v>
+        <v>70.78947368421052</v>
       </c>
       <c r="AS13" t="n">
-        <v>2526190.476190476</v>
+        <v>2486842.105263158</v>
       </c>
       <c r="AT13" t="n">
-        <v>74.0952380952381</v>
+        <v>74.21052631578948</v>
       </c>
       <c r="AU13" t="n">
-        <v>23.94117647058824</v>
+        <v>24.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>180.2352941176471</v>
+        <v>178.85</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.588235294117647</v>
+        <v>1.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>77.47058823529412</v>
+        <v>78.75</v>
       </c>
       <c r="AY13" t="n">
-        <v>25211764.70588235</v>
+        <v>31255000</v>
       </c>
       <c r="AZ13" t="n">
-        <v>83.11764705882354</v>
+        <v>83.55</v>
       </c>
       <c r="BA13" t="n">
         <v>26.83333333333333</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75024</v>
+        <v>66000</v>
       </c>
       <c r="F14" t="n">
         <v>75000</v>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>CQTUFgP</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>f3ddUIX</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>MDhPV0R</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>KUx4Q7x</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="W15" t="n">
@@ -3763,25 +3763,25 @@
         <v>78.625</v>
       </c>
       <c r="BA15" t="n">
-        <v>26.375</v>
+        <v>25.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>183.875</v>
+        <v>183.8333333333333</v>
       </c>
       <c r="BC15" t="n">
         <v>1</v>
       </c>
       <c r="BD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>566</v>
+        <v>422</v>
       </c>
       <c r="BF15" t="n">
-        <v>17700000</v>
+        <v>12700000</v>
       </c>
       <c r="BG15" t="n">
-        <v>589</v>
+        <v>443</v>
       </c>
       <c r="BH15" t="n">
         <v>23.75</v>
@@ -3880,12 +3880,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>vZA6VYp</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Q1njn0V</t>
+          <t>Q1njn0Vm</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -3929,22 +3929,22 @@
         <v>78.81818181818181</v>
       </c>
       <c r="AI16" t="n">
-        <v>24.2</v>
+        <v>24.90909090909091</v>
       </c>
       <c r="AJ16" t="n">
-        <v>183.7</v>
+        <v>184.7272727272727</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AL16" t="n">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="AM16" t="n">
-        <v>21930000</v>
+        <v>20190909.09090909</v>
       </c>
       <c r="AN16" t="n">
-        <v>82.59999999999999</v>
+        <v>81.90909090909091</v>
       </c>
       <c r="AO16" t="n">
         <v>25.14285714285714</v>
@@ -4100,12 +4100,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>M5BRZDs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>UgdQz0f</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -4131,58 +4131,58 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>25.27272727272727</v>
+        <v>25.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>184.5454545454545</v>
+        <v>184.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.636363636363636</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>76.18181818181819</v>
+        <v>75.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>10927272.72727273</v>
+        <v>9870000</v>
       </c>
       <c r="AH17" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>24.7</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AJ17" t="n">
-        <v>184.7</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.9</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AL17" t="n">
-        <v>78.3</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="AM17" t="n">
-        <v>17550000</v>
+        <v>17500000</v>
       </c>
       <c r="AN17" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="n">
-        <v>26.26086956521739</v>
+        <v>25.4</v>
       </c>
       <c r="AP17" t="n">
-        <v>182.695652173913</v>
+        <v>183.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.565217391304348</v>
+        <v>1.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>6639130.434782608</v>
+        <v>7440000</v>
       </c>
       <c r="AT17" t="n">
-        <v>76.34782608695652</v>
+        <v>77.3</v>
       </c>
       <c r="AU17" t="n">
         <v>23.57894736842105</v>
@@ -4203,25 +4203,25 @@
         <v>79.26315789473684</v>
       </c>
       <c r="BA17" t="n">
-        <v>25.33333333333333</v>
+        <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>185.6666666666667</v>
+        <v>183</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE17" t="n">
-        <v>214</v>
+        <v>139</v>
       </c>
       <c r="BF17" t="n">
-        <v>16150000</v>
+        <v>12450000</v>
       </c>
       <c r="BG17" t="n">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="BH17" t="n">
         <v>24.2</v>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>50000</v>
+        <v>43000</v>
       </c>
       <c r="F18" t="n">
         <v>50000</v>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>lGJdeem</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>v9WoiHG</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="W18" t="n">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>l0fHXMd</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>4ljanuk</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="W19" t="n">
@@ -4599,22 +4599,22 @@
         <v>75.09090909090909</v>
       </c>
       <c r="AO19" t="n">
-        <v>25.72222222222222</v>
+        <v>25.68421052631579</v>
       </c>
       <c r="AP19" t="n">
-        <v>184.5555555555555</v>
+        <v>184.8421052631579</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="AR19" t="n">
-        <v>73.05555555555556</v>
+        <v>73</v>
       </c>
       <c r="AS19" t="n">
-        <v>5122222.222222222</v>
+        <v>4978947.368421053</v>
       </c>
       <c r="AT19" t="n">
-        <v>75.72222222222223</v>
+        <v>75.68421052631579</v>
       </c>
       <c r="AU19" t="n">
         <v>26.25</v>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>47069</v>
+        <v>40000</v>
       </c>
       <c r="F20" t="n">
         <v>47069</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>pfoInmc</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>4fuCGs9</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="W20" t="n">
@@ -4855,25 +4855,25 @@
         <v>74.78260869565217</v>
       </c>
       <c r="BA20" t="n">
-        <v>23.33333333333333</v>
+        <v>22.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>177.3333333333333</v>
+        <v>176.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE20" t="n">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="BF20" t="n">
-        <v>140000000</v>
+        <v>89500000</v>
       </c>
       <c r="BG20" t="n">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="BH20" t="n">
         <v>24.66666666666667</v>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2VSFgl3</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>GzfvcwR</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="W21" t="n">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>185.1818181818182</v>
+        <v>186</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.727272727272727</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>74.36363636363636</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>6445454.545454546</v>
+        <v>6490000</v>
       </c>
       <c r="AH21" t="n">
-        <v>76.81818181818181</v>
+        <v>76.8</v>
       </c>
       <c r="AI21" t="n">
         <v>24.09090909090909</v>
@@ -5035,40 +5035,40 @@
         <v>79.81818181818181</v>
       </c>
       <c r="AO21" t="n">
-        <v>23.38095238095238</v>
+        <v>23.36842105263158</v>
       </c>
       <c r="AP21" t="n">
-        <v>185.3333333333333</v>
+        <v>185.578947368421</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.095238095238095</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AR21" t="n">
-        <v>71.57142857142857</v>
+        <v>71.42105263157895</v>
       </c>
       <c r="AS21" t="n">
-        <v>4432142.857142857</v>
+        <v>4351315.789473685</v>
       </c>
       <c r="AT21" t="n">
-        <v>77.47619047619048</v>
+        <v>77.42105263157895</v>
       </c>
       <c r="AU21" t="n">
-        <v>24.28571428571428</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AV21" t="n">
-        <v>182.9047619047619</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.142857142857143</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX21" t="n">
-        <v>72.42857142857143</v>
+        <v>73</v>
       </c>
       <c r="AY21" t="n">
-        <v>5815476.19047619</v>
+        <v>6501388.888888889</v>
       </c>
       <c r="AZ21" t="n">
-        <v>76.04761904761905</v>
+        <v>76.72222222222223</v>
       </c>
       <c r="BA21" t="n">
         <v>25.16666666666667</v>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>zyLSrbZ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>zyLSrbZ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>WvI4Hnn</t>
+          <t>WvI4Hnn1</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>54600</v>
+        <v>47000</v>
       </c>
       <c r="F24" t="n">
         <v>50028</v>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>IgZoGKF</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -5561,22 +5561,22 @@
         <v>72.90909090909091</v>
       </c>
       <c r="AI24" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>179.8888888888889</v>
+        <v>179.7</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>68.66666666666667</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AM24" t="n">
-        <v>1994444.444444444</v>
+        <v>1465000</v>
       </c>
       <c r="AN24" t="n">
-        <v>71.44444444444444</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AO24" t="n">
         <v>24.375</v>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>8E8qmw3</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>OzPMRhK</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>8E86CPu</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>57274</v>
+        <v>49000</v>
       </c>
       <c r="F27" t="n">
         <v>55800</v>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>EDRZkDz</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>YmfcAeC</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="W27" t="n">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>t0ZPdkU</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>A15eUM4</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="W28" t="n">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>UyNNTYW</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0AI1QUJ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2BYSk4K</t>
+          <t>2BYSk4KO</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>SQrxFAM</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -6683,22 +6683,22 @@
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>25.54545454545455</v>
+        <v>25.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>184.0909090909091</v>
+        <v>183.5</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>68.54545454545455</v>
+        <v>68.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1638636.363636364</v>
+        <v>1692500</v>
       </c>
       <c r="AH30" t="n">
-        <v>71.54545454545455</v>
+        <v>71.8</v>
       </c>
       <c r="AI30" t="n">
         <v>24.36363636363636</v>
@@ -6719,22 +6719,22 @@
         <v>71.72727272727273</v>
       </c>
       <c r="AO30" t="n">
-        <v>25.8695652173913</v>
+        <v>25.68181818181818</v>
       </c>
       <c r="AP30" t="n">
-        <v>182.7826086956522</v>
+        <v>182.4545454545455</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
       </c>
       <c r="AR30" t="n">
-        <v>67.52173913043478</v>
+        <v>67.45454545454545</v>
       </c>
       <c r="AS30" t="n">
-        <v>1417173.913043478</v>
+        <v>1431590.909090909</v>
       </c>
       <c r="AT30" t="n">
-        <v>70.26086956521739</v>
+        <v>70.31818181818181</v>
       </c>
       <c r="AU30" t="n">
         <v>26.29166666666667</v>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>v12aAJd</t>
+          <t>v12aAJdR</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -6903,22 +6903,22 @@
         <v>75.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>25.08333333333333</v>
+        <v>25.95238095238095</v>
       </c>
       <c r="AP31" t="n">
-        <v>184.4583333333333</v>
+        <v>182.952380952381</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>65.875</v>
+        <v>67.28571428571429</v>
       </c>
       <c r="AS31" t="n">
-        <v>1358333.333333333</v>
+        <v>1509523.809523809</v>
       </c>
       <c r="AT31" t="n">
-        <v>69.91666666666667</v>
+        <v>70.04761904761905</v>
       </c>
       <c r="AU31" t="n">
         <v>28.05263157894737</v>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>QHesBmS</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SQrxFAM</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="W33" t="n">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>OzPMRhK</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>t0ZPdkU</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="W34" t="n">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>QHesBmS</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="W35" t="n">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>A15eUM4</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>74667</v>
+        <v>71000</v>
       </c>
       <c r="F37" t="n">
         <v>67144</v>
@@ -7984,12 +7984,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>v12aAJd</t>
+          <t>v12aAJdR</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2BYSk4K</t>
+          <t>2BYSk4KO</t>
         </is>
       </c>
       <c r="W37" t="n">
@@ -8061,22 +8061,22 @@
         <v>73.30434782608695</v>
       </c>
       <c r="AU37" t="n">
-        <v>26.25</v>
+        <v>26.05263157894737</v>
       </c>
       <c r="AV37" t="n">
-        <v>182.2</v>
+        <v>181.7894736842105</v>
       </c>
       <c r="AW37" t="n">
         <v>1</v>
       </c>
       <c r="AX37" t="n">
-        <v>67.84999999999999</v>
+        <v>67.78947368421052</v>
       </c>
       <c r="AY37" t="n">
-        <v>1513500</v>
+        <v>1535263.157894737</v>
       </c>
       <c r="AZ37" t="n">
-        <v>71.15000000000001</v>
+        <v>71.26315789473684</v>
       </c>
       <c r="BA37" t="inlineStr"/>
       <c r="BB37" t="inlineStr"/>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>YmfcAeC</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>8E8qmw3</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="W38" t="n">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>62271</v>
+        <v>50000</v>
       </c>
       <c r="F39" t="n">
         <v>61833</v>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>UyNNTYW</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="W39" t="n">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>IgZoGKF</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>8E86CPu</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="W40" t="n">
@@ -8575,22 +8575,22 @@
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>24.77777777777778</v>
+        <v>25.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>181</v>
+        <v>180.7</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AG40" t="n">
-        <v>2066666.666666667</v>
+        <v>1530000</v>
       </c>
       <c r="AH40" t="n">
-        <v>72</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AI40" t="n">
         <v>24.27272727272727</v>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0AI1QUJ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>EDRZkDz</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -9035,6 +9035,208 @@
       <c r="BM42" t="inlineStr"/>
       <c r="BN42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>GfN42CgJ</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45437.625</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>74322</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M43" t="n">
+        <v>35</v>
+      </c>
+      <c r="N43" t="n">
+        <v>65</v>
+      </c>
+      <c r="O43" t="n">
+        <v>8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="n">
+        <v>8</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>59</v>
+      </c>
+      <c r="X43" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>20232024</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>182.9090909090909</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1475000</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>44700000</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>26.34782608695652</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>180.4782608695652</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>68.34782608695652</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1621521.739130435</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>70.82608695652173</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>22.81818181818182</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>180.9090909090909</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>78.68181818181819</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>29159090.90909091</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>83.90909090909091</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>136</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>3125000</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>143</v>
+      </c>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
